--- a/data/trans_orig/IP18E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18E-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81373</t>
+          <t>81679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92545</t>
+          <t>92621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>84177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>89406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>166787</t>
+          <t>166433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>177421</t>
+          <t>177558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54961</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61866</t>
+          <t>61868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60889</t>
+          <t>61475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119170</t>
+          <t>118984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127485</t>
+          <t>127114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57651</t>
+          <t>57228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>65176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56240</t>
+          <t>56330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63845</t>
+          <t>63874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117424</t>
+          <t>117559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127641</t>
+          <t>127802</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54835</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>60296</t>
+          <t>60299</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47926</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43531</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>87343</t>
+          <t>87599</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>96197</t>
+          <t>96396</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>102106</t>
+          <t>102408</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>112787</t>
+          <t>113420</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>106850</t>
+          <t>106147</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>116480</t>
+          <t>116475</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>213309</t>
+          <t>213604</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>227825</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,82 +4957,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>7888</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>5343</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>3779</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>8135</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>109657</t>
+          <t>110057</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>117268</t>
+          <t>117383</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>122245</t>
+          <t>122106</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128995</t>
+          <t>128993</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>235150</t>
+          <t>234841</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>245082</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>51125</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>50911</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>559408</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>579694</t>
+          <t>579792</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1106523</t>
+          <t>1106063</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1134395</t>
+          <t>1134911</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53390</t>
+          <t>53411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56451</t>
+          <t>56870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61540</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>106194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>114198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83529</t>
+          <t>83591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91970</t>
+          <t>92158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83916</t>
+          <t>83712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93362</t>
+          <t>93394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>171642</t>
+          <t>170639</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>184166</t>
+          <t>183680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7341,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>734</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63761</t>
+          <t>63774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>62705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122315</t>
+          <t>121764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131468</t>
+          <t>131563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71903</t>
+          <t>71911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>144323</t>
+          <t>144512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150456</t>
+          <t>150459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41937</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>74857</t>
+          <t>74668</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>81397</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>433</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -9161,12 +9161,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9274,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54518</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>57398</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>102600</t>
+          <t>103094</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>110990</t>
+          <t>111171</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -9617,12 +9617,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -9730,12 +9730,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9745,82 +9745,82 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>3867</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>9639</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>5675</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>15493</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>3867</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>8149</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>9639</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>5299</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>15618</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9843,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>115985</t>
+          <t>114863</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>126257</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>129004</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>138471</t>
+          <t>139145</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>248781</t>
+          <t>248746</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>262778</t>
+          <t>263185</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>140435</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>148560</t>
+          <t>148441</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>143346</t>
+          <t>142518</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>153038</t>
+          <t>153375</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>286476</t>
+          <t>287856</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>299460</t>
+          <t>299732</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -10755,12 +10755,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10805,12 +10805,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10868,12 +10868,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>661538</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>682374</t>
+          <t>682051</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1290435</t>
+          <t>1291657</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1318748</t>
+          <t>1317988</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -11673,12 +11673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11786,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>49207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55432</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92803</t>
+          <t>92388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103316</t>
+          <t>103180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -12242,12 +12242,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -12355,12 +12355,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83292</t>
+          <t>84068</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89172</t>
+          <t>89190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>89656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176204</t>
+          <t>175953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182970</t>
+          <t>182915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12861,12 +12861,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12896,12 +12896,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58145</t>
+          <t>57542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65216</t>
+          <t>65224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12939,12 +12939,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52925</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60190</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12974,12 +12974,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113728</t>
+          <t>113551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124186</t>
+          <t>123903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13352,12 +13352,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13415,12 +13415,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13430,12 +13430,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71212</t>
+          <t>71176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67297</t>
+          <t>67882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75706</t>
+          <t>75791</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136291</t>
+          <t>136005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145945</t>
+          <t>145721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -13949,12 +13949,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -14062,12 +14062,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14077,12 +14077,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40647</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>80102</t>
+          <t>79720</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>85470</t>
+          <t>85468</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14588,12 +14588,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>46412</t>
+          <t>46556</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14701,12 +14701,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>95515</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103393</t>
+          <t>103368</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14716,12 +14716,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -15087,12 +15087,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -15200,12 +15200,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100375</t>
+          <t>100716</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>108729</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>105614</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>112187</t>
+          <t>112202</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>209343</t>
+          <t>208926</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>219390</t>
+          <t>219064</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -15543,12 +15543,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15558,12 +15558,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15613,12 +15613,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15628,12 +15628,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -15656,12 +15656,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15691,12 +15691,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15741,12 +15741,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -15769,12 +15769,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>141860</t>
+          <t>141521</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>152155</t>
+          <t>151923</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15784,12 +15784,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>143418</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>154902</t>
+          <t>154813</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15819,12 +15819,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15839,12 +15839,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>290174</t>
+          <t>287970</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>305638</t>
+          <t>304309</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -16225,12 +16225,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16240,12 +16240,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>71207</t>
+          <t>71711</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16310,12 +16310,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -16338,12 +16338,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -16373,12 +16373,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16408,12 +16408,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16423,12 +16423,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -16992,7 +16992,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17100,12 +17100,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17115,12 +17115,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -17143,12 +17143,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -17213,12 +17213,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -17712,7 +17712,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -18055,12 +18055,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -18070,12 +18070,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18125,12 +18125,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18140,12 +18140,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -18281,12 +18281,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -18742,7 +18742,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -18920,12 +18920,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -18935,12 +18935,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19346,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -19469,7 +19469,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -19504,12 +19504,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -20331,12 +20331,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -20346,12 +20346,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -20366,12 +20366,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -20381,12 +20381,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -20416,12 +20416,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20514,12 +20514,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -20529,12 +20529,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -20557,12 +20557,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20572,12 +20572,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20592,12 +20592,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20607,12 +20607,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20627,12 +20627,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>29210</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42976</t>
+          <t>43243</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20642,12 +20642,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -21141,7 +21141,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -21469,12 +21469,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -21484,12 +21484,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21519,12 +21519,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21539,12 +21539,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21554,12 +21554,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -21582,12 +21582,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21597,12 +21597,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21617,12 +21617,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21632,12 +21632,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21652,12 +21652,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21667,12 +21667,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -21695,12 +21695,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21710,12 +21710,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21730,12 +21730,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21745,12 +21745,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21765,12 +21765,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
